--- a/output/Tables/2019/Monte Carlo/HIA_per_disease_Rubin.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_disease_Rubin.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>58576.533</v>
+        <v>58493.664</v>
       </c>
       <c r="C2">
-        <v>55680.698</v>
+        <v>55613.252</v>
       </c>
       <c r="D2">
-        <v>61472.367</v>
+        <v>61374.075</v>
       </c>
       <c r="E2">
-        <v>605500.126</v>
+        <v>604826.063</v>
       </c>
       <c r="F2">
-        <v>587624.0209999999</v>
+        <v>587001.505</v>
       </c>
       <c r="G2">
-        <v>623376.23</v>
+        <v>622650.621</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>80531516702.45399</v>
+        <v>80441866393.543</v>
       </c>
       <c r="L2">
-        <v>78153994837.692</v>
+        <v>78071200129.427</v>
       </c>
       <c r="M2">
-        <v>82909038567.215</v>
+        <v>82812532657.658</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>40192.88</v>
+        <v>40109.648</v>
       </c>
       <c r="C3">
-        <v>38427.133</v>
+        <v>38359.282</v>
       </c>
       <c r="D3">
-        <v>41958.627</v>
+        <v>41860.015</v>
       </c>
       <c r="E3">
-        <v>35956.855</v>
+        <v>35900.387</v>
       </c>
       <c r="F3">
-        <v>34526.689</v>
+        <v>34482.905</v>
       </c>
       <c r="G3">
-        <v>37387.022</v>
+        <v>37317.868</v>
       </c>
       <c r="H3">
-        <v>2238823795.023</v>
+        <v>2234187637.416</v>
       </c>
       <c r="I3">
-        <v>2140468152.233</v>
+        <v>2136688699.354</v>
       </c>
       <c r="J3">
-        <v>2337179437.813</v>
+        <v>2331686575.478</v>
       </c>
       <c r="K3">
-        <v>4782261781.281</v>
+        <v>4774751428.058</v>
       </c>
       <c r="L3">
-        <v>4592049605.668</v>
+        <v>4586226351.457</v>
       </c>
       <c r="M3">
-        <v>4972473956.894</v>
+        <v>4963276504.659</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>31006.032</v>
+        <v>31205.641</v>
       </c>
       <c r="C4">
-        <v>29410.098</v>
+        <v>29729.992</v>
       </c>
       <c r="D4">
-        <v>32601.966</v>
+        <v>32681.291</v>
       </c>
       <c r="E4">
-        <v>46613.335</v>
+        <v>46961.933</v>
       </c>
       <c r="F4">
-        <v>43786.643</v>
+        <v>44239.119</v>
       </c>
       <c r="G4">
-        <v>49440.028</v>
+        <v>49684.747</v>
       </c>
       <c r="H4">
-        <v>459106318.279</v>
+        <v>462061933.448</v>
       </c>
       <c r="I4">
-        <v>435475323.919</v>
+        <v>440211989.604</v>
       </c>
       <c r="J4">
-        <v>482737312.639</v>
+        <v>483911877.292</v>
       </c>
       <c r="K4">
-        <v>6199573608.049</v>
+        <v>6245937086.815</v>
       </c>
       <c r="L4">
-        <v>5823623457.847</v>
+        <v>5883802815.562</v>
       </c>
       <c r="M4">
-        <v>6575523758.252</v>
+        <v>6608071358.068</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>6396.197</v>
+        <v>6403.897</v>
       </c>
       <c r="C5">
-        <v>6066.985</v>
+        <v>6092.563</v>
       </c>
       <c r="D5">
-        <v>6725.408</v>
+        <v>6715.231</v>
       </c>
       <c r="E5">
-        <v>12497.836</v>
+        <v>12514.81</v>
       </c>
       <c r="F5">
-        <v>11838.514</v>
+        <v>11883.816</v>
       </c>
       <c r="G5">
-        <v>13157.159</v>
+        <v>13145.803</v>
       </c>
       <c r="H5">
-        <v>481000376.982</v>
+        <v>481579454.307</v>
       </c>
       <c r="I5">
-        <v>456243329.205</v>
+        <v>458166852.781</v>
       </c>
       <c r="J5">
-        <v>505757424.76</v>
+        <v>504992055.832</v>
       </c>
       <c r="K5">
-        <v>1662212232.008</v>
+        <v>1664469674.852</v>
       </c>
       <c r="L5">
-        <v>1574522331.359</v>
+        <v>1580547594.424</v>
       </c>
       <c r="M5">
-        <v>1749902132.657</v>
+        <v>1748391755.28</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>13973.364</v>
+        <v>13935.948</v>
       </c>
       <c r="C6">
-        <v>13089.37</v>
+        <v>13088.58</v>
       </c>
       <c r="D6">
-        <v>14857.358</v>
+        <v>14783.316</v>
       </c>
       <c r="E6">
-        <v>23256.136</v>
+        <v>23242.012</v>
       </c>
       <c r="F6">
-        <v>22103.86</v>
+        <v>22085.238</v>
       </c>
       <c r="G6">
-        <v>24408.411</v>
+        <v>24398.785</v>
       </c>
       <c r="H6">
-        <v>235297473.058</v>
+        <v>234667433.392</v>
       </c>
       <c r="I6">
-        <v>220411897.461</v>
+        <v>220398604.992</v>
       </c>
       <c r="J6">
-        <v>250183048.655</v>
+        <v>248936261.791</v>
       </c>
       <c r="K6">
-        <v>3093066040.554</v>
+        <v>3091187577.782</v>
       </c>
       <c r="L6">
-        <v>2939813356.363</v>
+        <v>2937336699.107</v>
       </c>
       <c r="M6">
-        <v>3246318724.746</v>
+        <v>3245038456.457</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>152005.037</v>
+        <v>151928.453</v>
       </c>
       <c r="C7">
-        <v>146429.295</v>
+        <v>146455.668</v>
       </c>
       <c r="D7">
-        <v>157580.78</v>
+        <v>157401.239</v>
       </c>
       <c r="E7">
-        <v>445423.739</v>
+        <v>17511.164</v>
       </c>
       <c r="F7">
-        <v>421949.245</v>
+        <v>16823.606</v>
       </c>
       <c r="G7">
-        <v>468898.232</v>
+        <v>18198.722</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>59241357221.791</v>
+        <v>2328984837.434</v>
       </c>
       <c r="L7">
-        <v>56119249613.637</v>
+        <v>2237539664.006</v>
       </c>
       <c r="M7">
-        <v>62363464829.946</v>
+        <v>2420430010.861</v>
       </c>
     </row>
     <row r="8">
@@ -686,40 +686,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>243573.51</v>
+        <v>243583.587</v>
       </c>
       <c r="C8">
-        <v>233422.881</v>
+        <v>233726.085</v>
       </c>
       <c r="D8">
-        <v>253724.139</v>
+        <v>253441.092</v>
       </c>
       <c r="E8">
-        <v>563747.901</v>
+        <v>136130.306</v>
       </c>
       <c r="F8">
-        <v>534204.951</v>
+        <v>129514.684</v>
       </c>
       <c r="G8">
-        <v>593290.852</v>
+        <v>142745.925</v>
       </c>
       <c r="H8">
-        <v>3414227963.342</v>
+        <v>3412496458.563</v>
       </c>
       <c r="I8">
-        <v>3252598702.818</v>
+        <v>3255466146.731</v>
       </c>
       <c r="J8">
-        <v>3575857223.867</v>
+        <v>3569526770.393</v>
       </c>
       <c r="K8">
-        <v>74978470883.683</v>
+        <v>18105330604.941</v>
       </c>
       <c r="L8">
-        <v>71049258364.87399</v>
+        <v>17225453124.556</v>
       </c>
       <c r="M8">
-        <v>78907683402.495</v>
+        <v>18985208085.325</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>302150.043</v>
+        <v>302077.251</v>
       </c>
       <c r="C9">
-        <v>289103.579</v>
+        <v>289339.337</v>
       </c>
       <c r="D9">
-        <v>315196.5060000001</v>
+        <v>314815.167</v>
       </c>
       <c r="E9">
-        <v>1169248.027</v>
+        <v>740956.3689999999</v>
       </c>
       <c r="F9">
-        <v>1121828.972</v>
+        <v>716516.189</v>
       </c>
       <c r="G9">
-        <v>1216667.082</v>
+        <v>765396.546</v>
       </c>
       <c r="H9">
-        <v>3414227963.342</v>
+        <v>3412496458.563</v>
       </c>
       <c r="I9">
-        <v>3252598702.818</v>
+        <v>3255466146.731</v>
       </c>
       <c r="J9">
-        <v>3575857223.867</v>
+        <v>3569526770.393</v>
       </c>
       <c r="K9">
-        <v>155509987586.137</v>
+        <v>98547196998.48401</v>
       </c>
       <c r="L9">
-        <v>149203253202.566</v>
+        <v>95296653253.98299</v>
       </c>
       <c r="M9">
-        <v>161816721969.71</v>
+        <v>101797740742.983</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Monte Carlo/HIA_per_disease_Rubin.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_disease_Rubin.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>58493.664</v>
+        <v>58494.288</v>
       </c>
       <c r="C2">
-        <v>55613.252</v>
+        <v>55613.417</v>
       </c>
       <c r="D2">
-        <v>61374.075</v>
+        <v>61375.159</v>
       </c>
       <c r="E2">
-        <v>604826.063</v>
+        <v>604892.097</v>
       </c>
       <c r="F2">
-        <v>587001.505</v>
+        <v>587055.503</v>
       </c>
       <c r="G2">
-        <v>622650.621</v>
+        <v>622728.692</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>80441866393.543</v>
+        <v>80450648928.94099</v>
       </c>
       <c r="L2">
-        <v>78071200129.427</v>
+        <v>78078381883.617</v>
       </c>
       <c r="M2">
-        <v>82812532657.658</v>
+        <v>82822915974.26401</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>40109.648</v>
+        <v>40151.634</v>
       </c>
       <c r="C3">
-        <v>38359.282</v>
+        <v>38400.342</v>
       </c>
       <c r="D3">
-        <v>41860.015</v>
+        <v>41902.927</v>
       </c>
       <c r="E3">
-        <v>35900.387</v>
+        <v>35944.137</v>
       </c>
       <c r="F3">
-        <v>34482.905</v>
+        <v>34526.475</v>
       </c>
       <c r="G3">
-        <v>37317.868</v>
+        <v>37361.799</v>
       </c>
       <c r="H3">
-        <v>2234187637.416</v>
+        <v>2236526326.502</v>
       </c>
       <c r="I3">
-        <v>2136688699.354</v>
+        <v>2138975836.899</v>
       </c>
       <c r="J3">
-        <v>2331686575.478</v>
+        <v>2334076816.105</v>
       </c>
       <c r="K3">
-        <v>4774751428.058</v>
+        <v>4780570189.285</v>
       </c>
       <c r="L3">
-        <v>4586226351.457</v>
+        <v>4592021177.518</v>
       </c>
       <c r="M3">
-        <v>4963276504.659</v>
+        <v>4969119201.052</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>31205.641</v>
+        <v>31236.759</v>
       </c>
       <c r="C4">
-        <v>29729.992</v>
+        <v>29749.866</v>
       </c>
       <c r="D4">
-        <v>32681.291</v>
+        <v>32723.653</v>
       </c>
       <c r="E4">
-        <v>46961.933</v>
+        <v>47101.692</v>
       </c>
       <c r="F4">
-        <v>44239.119</v>
+        <v>44355.301</v>
       </c>
       <c r="G4">
-        <v>49684.747</v>
+        <v>49848.083</v>
       </c>
       <c r="H4">
-        <v>462061933.448</v>
+        <v>462522697.682</v>
       </c>
       <c r="I4">
-        <v>440211989.604</v>
+        <v>440506268.072</v>
       </c>
       <c r="J4">
-        <v>483911877.292</v>
+        <v>484539127.293</v>
       </c>
       <c r="K4">
-        <v>6245937086.815</v>
+        <v>6264525079.272</v>
       </c>
       <c r="L4">
-        <v>5883802815.562</v>
+        <v>5899255086.525</v>
       </c>
       <c r="M4">
-        <v>6608071358.068</v>
+        <v>6629795072.019</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>6403.897</v>
+        <v>6404.958</v>
       </c>
       <c r="C5">
-        <v>6092.563</v>
+        <v>6093.188</v>
       </c>
       <c r="D5">
-        <v>6715.231</v>
+        <v>6716.728</v>
       </c>
       <c r="E5">
-        <v>12514.81</v>
+        <v>12504.519</v>
       </c>
       <c r="F5">
-        <v>11883.816</v>
+        <v>11870.199</v>
       </c>
       <c r="G5">
-        <v>13145.803</v>
+        <v>13138.839</v>
       </c>
       <c r="H5">
-        <v>481579454.307</v>
+        <v>481659263.373</v>
       </c>
       <c r="I5">
-        <v>458166852.781</v>
+        <v>458213842.177</v>
       </c>
       <c r="J5">
-        <v>504992055.832</v>
+        <v>505104684.568</v>
       </c>
       <c r="K5">
-        <v>1664469674.852</v>
+        <v>1663101048.418</v>
       </c>
       <c r="L5">
-        <v>1580547594.424</v>
+        <v>1578736472.331</v>
       </c>
       <c r="M5">
-        <v>1748391755.28</v>
+        <v>1747465624.505</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>13935.948</v>
+        <v>13935.46</v>
       </c>
       <c r="C6">
-        <v>13088.58</v>
+        <v>13088.821</v>
       </c>
       <c r="D6">
-        <v>14783.316</v>
+        <v>14782.1</v>
       </c>
       <c r="E6">
-        <v>23242.012</v>
+        <v>23252.58</v>
       </c>
       <c r="F6">
-        <v>22085.238</v>
+        <v>22098.172</v>
       </c>
       <c r="G6">
-        <v>24398.785</v>
+        <v>24406.988</v>
       </c>
       <c r="H6">
-        <v>234667433.392</v>
+        <v>234659214.651</v>
       </c>
       <c r="I6">
-        <v>220398604.992</v>
+        <v>220402650.514</v>
       </c>
       <c r="J6">
-        <v>248936261.791</v>
+        <v>248915778.788</v>
       </c>
       <c r="K6">
-        <v>3091187577.782</v>
+        <v>3092593143.733</v>
       </c>
       <c r="L6">
-        <v>2937336699.107</v>
+        <v>2939056873.721</v>
       </c>
       <c r="M6">
-        <v>3245038456.457</v>
+        <v>3246129413.745</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>151928.453</v>
+        <v>126008.848</v>
       </c>
       <c r="C7">
-        <v>146455.668</v>
+        <v>121264.534</v>
       </c>
       <c r="D7">
-        <v>157401.239</v>
+        <v>130753.163</v>
       </c>
       <c r="E7">
-        <v>17511.164</v>
+        <v>41036.118</v>
       </c>
       <c r="F7">
-        <v>16823.606</v>
+        <v>38886.047</v>
       </c>
       <c r="G7">
-        <v>18198.722</v>
+        <v>43186.189</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>2328984837.434</v>
+        <v>5457803706.637</v>
       </c>
       <c r="L7">
-        <v>2237539664.006</v>
+        <v>5171844281.957</v>
       </c>
       <c r="M7">
-        <v>2420430010.861</v>
+        <v>5743763131.317</v>
       </c>
     </row>
     <row r="8">
@@ -686,40 +686,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>243583.587</v>
+        <v>217737.659</v>
       </c>
       <c r="C8">
-        <v>233726.085</v>
+        <v>208596.751</v>
       </c>
       <c r="D8">
-        <v>253441.092</v>
+        <v>226878.571</v>
       </c>
       <c r="E8">
-        <v>136130.306</v>
+        <v>159839.046</v>
       </c>
       <c r="F8">
-        <v>129514.684</v>
+        <v>151736.194</v>
       </c>
       <c r="G8">
-        <v>142745.925</v>
+        <v>167941.898</v>
       </c>
       <c r="H8">
-        <v>3412496458.563</v>
+        <v>3415367502.208</v>
       </c>
       <c r="I8">
-        <v>3255466146.731</v>
+        <v>3258098597.662</v>
       </c>
       <c r="J8">
-        <v>3569526770.393</v>
+        <v>3572636406.754</v>
       </c>
       <c r="K8">
-        <v>18105330604.941</v>
+        <v>21258593167.345</v>
       </c>
       <c r="L8">
-        <v>17225453124.556</v>
+        <v>20180913892.052</v>
       </c>
       <c r="M8">
-        <v>18985208085.325</v>
+        <v>22336272442.638</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>302077.251</v>
+        <v>276231.947</v>
       </c>
       <c r="C9">
-        <v>289339.337</v>
+        <v>264210.168</v>
       </c>
       <c r="D9">
-        <v>314815.167</v>
+        <v>288253.73</v>
       </c>
       <c r="E9">
-        <v>740956.3689999999</v>
+        <v>764731.1429999999</v>
       </c>
       <c r="F9">
-        <v>716516.189</v>
+        <v>738791.697</v>
       </c>
       <c r="G9">
-        <v>765396.546</v>
+        <v>790670.5900000001</v>
       </c>
       <c r="H9">
-        <v>3412496458.563</v>
+        <v>3415367502.208</v>
       </c>
       <c r="I9">
-        <v>3255466146.731</v>
+        <v>3258098597.662</v>
       </c>
       <c r="J9">
-        <v>3569526770.393</v>
+        <v>3572636406.754</v>
       </c>
       <c r="K9">
-        <v>98547196998.48401</v>
+        <v>101709242096.286</v>
       </c>
       <c r="L9">
-        <v>95296653253.98299</v>
+        <v>98259295775.66899</v>
       </c>
       <c r="M9">
-        <v>101797740742.983</v>
+        <v>105159188416.902</v>
       </c>
     </row>
   </sheetData>
